--- a/tests/samples/XLSX_files/extracted_pdf-expected_when_description_in_box.xlsx
+++ b/tests/samples/XLSX_files/extracted_pdf-expected_when_description_in_box.xlsx
@@ -464,10 +464,8 @@
           <t>BRACKET, MOUNTING, V-CLAMP, FD SERIES</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -491,10 +489,8 @@
           <t>Fiber Brkt Asm, 24 Pos, 3 Row, Hing, Pur</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C3" t="n">
+        <v>150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -518,10 +514,8 @@
           <t>Encl, Parking/Pass Through Module, Base</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="C4" t="n">
+        <v>160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -545,10 +539,8 @@
           <t>Encl, Base, AT&amp;T RM2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="C5" t="n">
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -572,10 +564,8 @@
           <t>Encl, 18.5x8.84, N4, SS, Ltch, KO,Bl,BK</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C6" t="n">
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -599,10 +589,8 @@
           <t>Encl, Cover, RM2, Black</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C7" t="n">
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -626,10 +614,8 @@
           <t>Bracket, Adapter, LC Duplex, 12 Port 3x4</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="C8" t="n">
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -653,10 +639,8 @@
           <t>Cover, Plastic, RM2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="C9" t="n">
+        <v>500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -680,10 +664,8 @@
           <t>Bracket, Mounting, 351-0154/351-0155</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="C10" t="n">
+        <v>500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -707,10 +689,8 @@
           <t>Back Panel, RSCAC-9556</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="C11" t="n">
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -734,10 +714,8 @@
           <t>Bracket, Step, 12 Position, Neutral</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="C12" t="n">
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -761,10 +739,8 @@
           <t>Back Panel, 14.17 x 7.75</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="C13" t="n">
+        <v>35</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -788,10 +764,8 @@
           <t>Back Panel, RMx-E2x-xxxMS-21NN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -815,10 +789,8 @@
           <t>Dome Pole Mnt, U-Bolt Part 1 w/Cutouts</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="C15" t="n">
+        <v>200</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -842,10 +814,8 @@
           <t>Faceplate, Front Left, RM2 Encl, Black</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C16" t="n">
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -869,10 +839,8 @@
           <t>Bracket, 19in MTG Ear A, RM2, Black</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C17" t="n">
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -896,10 +864,8 @@
           <t>Bracket, 19in MTG Ear B, RM2, Black</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C18" t="n">
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -923,10 +889,8 @@
           <t>Bracket, 23in MTG Ear A, RM2, Black</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C19" t="n">
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -950,10 +914,8 @@
           <t>Bracket, 23in MTG Ear B, RM2, Black</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C20" t="n">
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -977,10 +939,8 @@
           <t>Face Plate, RM2, Black</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C21" t="n">
+        <v>14</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1004,10 +964,8 @@
           <t>Harness, Alarm, RM3</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="C22" t="n">
+        <v>150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1031,10 +989,8 @@
           <t>Modular Rack, Ground Plate</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="C23" t="n">
+        <v>500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1058,10 +1014,8 @@
           <t>Modular Rack, Ground Plate, Black</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C24" t="n">
+        <v>14</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
